--- a/etf_holdings/2026-09-07_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-07_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,12 +571,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00981A(98,000)、00403A(100,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00403A(-50,000)、00400A(-33,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00400A(41,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00403A(-50,000)、00400A(-33,000)</t>
+          <t>00982A(-1,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,107 +644,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00400A(41,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00982A(-1,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>00982A(-3,000)、00403A(-500,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>00981A(555,000)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>00985A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00981A(-260,000)、00403A(-157,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-07_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-07_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,12 +571,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>00981A(98,000)、00403A(100,000)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00403A(-50,000)、00400A(-33,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,47 +614,137 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00400A(41,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00982A(-1,000)</t>
+          <t>00403A(-50,000)、00400A(-33,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00400A(41,000)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>00982A(-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>3711</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>日月光投控</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>00982A(-3,000)、00403A(-500,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00981A(555,000)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>00985A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>00981A(-260,000)、00403A(-157,000)</t>
         </is>
       </c>
     </row>
